--- a/Team-Data/2008-09/11-30-2008-09.xlsx
+++ b/Team-Data/2008-09/11-30-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -748,16 +815,16 @@
         <v>6</v>
       </c>
       <c r="AG2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
       </c>
       <c r="AI2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>20</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>18</v>
       </c>
       <c r="AK2" t="n">
         <v>14</v>
@@ -775,19 +842,19 @@
         <v>20</v>
       </c>
       <c r="AP2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ2" t="n">
         <v>23</v>
       </c>
       <c r="AR2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AU2" t="n">
         <v>14</v>
@@ -796,13 +863,13 @@
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ2" t="n">
         <v>14</v>
@@ -811,10 +878,10 @@
         <v>23</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -843,85 +910,85 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.882</v>
+        <v>0.889</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
       </c>
       <c r="I3" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="J3" t="n">
-        <v>75.8</v>
+        <v>75.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0.467</v>
+        <v>0.466</v>
       </c>
       <c r="L3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M3" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.343</v>
+        <v>0.337</v>
       </c>
       <c r="O3" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="P3" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.766</v>
+        <v>0.756</v>
       </c>
       <c r="R3" t="n">
         <v>10.3</v>
       </c>
       <c r="S3" t="n">
-        <v>32.6</v>
+        <v>32.2</v>
       </c>
       <c r="T3" t="n">
-        <v>42.9</v>
+        <v>42.5</v>
       </c>
       <c r="U3" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="V3" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="W3" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.9</v>
+        <v>23.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>98.7</v>
+        <v>98.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -933,10 +1000,10 @@
         <v>2</v>
       </c>
       <c r="AH3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
@@ -948,10 +1015,10 @@
         <v>20</v>
       </c>
       <c r="AM3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO3" t="n">
         <v>2</v>
@@ -960,40 +1027,40 @@
         <v>4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR3" t="n">
         <v>23</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
         <v>11</v>
       </c>
       <c r="AV3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA3" t="n">
         <v>3</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC3" t="n">
         <v>3</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -1127,16 +1194,16 @@
         <v>25</v>
       </c>
       <c r="AL4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP4" t="n">
         <v>11</v>
@@ -1148,7 +1215,7 @@
         <v>19</v>
       </c>
       <c r="AS4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT4" t="n">
         <v>28</v>
@@ -1166,13 +1233,13 @@
         <v>20</v>
       </c>
       <c r="AY4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ4" t="n">
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -1222,67 +1289,67 @@
         <v>48</v>
       </c>
       <c r="I5" t="n">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="J5" t="n">
-        <v>84.5</v>
+        <v>84.3</v>
       </c>
       <c r="K5" t="n">
         <v>0.43</v>
       </c>
       <c r="L5" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="M5" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.36</v>
+        <v>0.352</v>
       </c>
       <c r="O5" t="n">
-        <v>19.1</v>
+        <v>19.9</v>
       </c>
       <c r="P5" t="n">
-        <v>23.5</v>
+        <v>24.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="R5" t="n">
-        <v>12.1</v>
+        <v>12.6</v>
       </c>
       <c r="S5" t="n">
-        <v>30.6</v>
+        <v>30</v>
       </c>
       <c r="T5" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="U5" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="V5" t="n">
-        <v>15.4</v>
+        <v>15.7</v>
       </c>
       <c r="W5" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X5" t="n">
         <v>5.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="Z5" t="n">
         <v>23.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.6</v>
+        <v>21.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>97.5</v>
+        <v>97.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.4</v>
+        <v>-3.3</v>
       </c>
       <c r="AD5" t="n">
         <v>15</v>
@@ -1303,46 +1370,46 @@
         <v>14</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO5" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AP5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR5" t="n">
         <v>6</v>
       </c>
       <c r="AS5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AT5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX5" t="n">
         <v>17</v>
@@ -1354,7 +1421,7 @@
         <v>26</v>
       </c>
       <c r="BA5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BB5" t="n">
         <v>17</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -1389,91 +1456,91 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
         <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.875</v>
+        <v>0.824</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>38.7</v>
+        <v>38.1</v>
       </c>
       <c r="J6" t="n">
-        <v>80</v>
+        <v>79.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.484</v>
+        <v>0.481</v>
       </c>
       <c r="L6" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="M6" t="n">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.346</v>
+        <v>0.339</v>
       </c>
       <c r="O6" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="P6" t="n">
-        <v>26.3</v>
+        <v>26.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.772</v>
+        <v>0.769</v>
       </c>
       <c r="R6" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="S6" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="T6" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="U6" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="V6" t="n">
-        <v>12.4</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
         <v>7.4</v>
       </c>
       <c r="X6" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.1</v>
+        <v>21.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>104.8</v>
+        <v>103.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>11.9</v>
+        <v>10.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG6" t="n">
         <v>3</v>
@@ -1482,10 +1549,10 @@
         <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AK6" t="n">
         <v>3</v>
@@ -1494,52 +1561,52 @@
         <v>10</v>
       </c>
       <c r="AM6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AO6" t="n">
         <v>6</v>
       </c>
       <c r="AP6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS6" t="n">
         <v>10</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AT6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU6" t="n">
         <v>12</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AV6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>13</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>12</v>
       </c>
       <c r="BA6" t="n">
         <v>13</v>
       </c>
       <c r="BB6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC6" t="n">
         <v>2</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -1652,28 +1719,28 @@
         <v>15</v>
       </c>
       <c r="AE7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH7" t="n">
         <v>10</v>
       </c>
       <c r="AI7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK7" t="n">
         <v>20</v>
       </c>
       <c r="AL7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM7" t="n">
         <v>10</v>
@@ -1685,7 +1752,7 @@
         <v>18</v>
       </c>
       <c r="AP7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ7" t="n">
         <v>5</v>
@@ -1697,7 +1764,7 @@
         <v>1</v>
       </c>
       <c r="AT7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU7" t="n">
         <v>14</v>
@@ -1721,10 +1788,10 @@
         <v>27</v>
       </c>
       <c r="BB7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -1753,85 +1820,85 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8" t="n">
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.667</v>
+        <v>0.647</v>
       </c>
       <c r="H8" t="n">
         <v>48.3</v>
       </c>
       <c r="I8" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="J8" t="n">
         <v>77.59999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L8" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="M8" t="n">
-        <v>16.6</v>
+        <v>16.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0.329</v>
+        <v>0.316</v>
       </c>
       <c r="O8" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="P8" t="n">
-        <v>31.6</v>
+        <v>32.1</v>
       </c>
       <c r="Q8" t="n">
         <v>0.78</v>
       </c>
       <c r="R8" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S8" t="n">
         <v>31</v>
       </c>
       <c r="T8" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U8" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="V8" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="W8" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="X8" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="Y8" t="n">
         <v>6.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>24.9</v>
+        <v>25.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>100.6</v>
+        <v>100.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1843,25 +1910,25 @@
         <v>6</v>
       </c>
       <c r="AH8" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AI8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>24</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>25</v>
       </c>
       <c r="AK8" t="n">
         <v>11</v>
       </c>
       <c r="AL8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AM8" t="n">
         <v>19</v>
       </c>
-      <c r="AM8" t="n">
-        <v>17</v>
-      </c>
       <c r="AN8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1876,13 +1943,13 @@
         <v>24</v>
       </c>
       <c r="AS8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV8" t="n">
         <v>26</v>
@@ -1891,22 +1958,22 @@
         <v>2</v>
       </c>
       <c r="AX8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AY8" t="n">
         <v>28</v>
       </c>
       <c r="AZ8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -1935,70 +2002,70 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="J9" t="n">
-        <v>78.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L9" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="M9" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.386</v>
+        <v>0.393</v>
       </c>
       <c r="O9" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="P9" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.768</v>
+        <v>0.765</v>
       </c>
       <c r="R9" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="S9" t="n">
-        <v>29.6</v>
+        <v>30.2</v>
       </c>
       <c r="T9" t="n">
-        <v>40.9</v>
+        <v>41.7</v>
       </c>
       <c r="U9" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V9" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="W9" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="X9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="Z9" t="n">
         <v>21.7</v>
@@ -2007,88 +2074,88 @@
         <v>21.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>96.7</v>
+        <v>97.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AE9" t="n">
         <v>10</v>
       </c>
       <c r="AF9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH9" t="n">
         <v>21</v>
       </c>
       <c r="AI9" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AJ9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AK9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL9" t="n">
         <v>16</v>
       </c>
       <c r="AM9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV9" t="n">
         <v>6</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>5</v>
       </c>
       <c r="AW9" t="n">
         <v>23</v>
       </c>
       <c r="AX9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AY9" t="n">
         <v>13</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA9" t="n">
         <v>12</v>
       </c>
       <c r="BB9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BC9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2262,13 @@
         <v>-4.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG10" t="n">
         <v>24</v>
@@ -2210,7 +2277,7 @@
         <v>7</v>
       </c>
       <c r="AI10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ10" t="n">
         <v>3</v>
@@ -2222,7 +2289,7 @@
         <v>18</v>
       </c>
       <c r="AM10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN10" t="n">
         <v>27</v>
@@ -2240,13 +2307,13 @@
         <v>3</v>
       </c>
       <c r="AS10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV10" t="n">
         <v>17</v>
@@ -2258,16 +2325,16 @@
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ10" t="n">
         <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC10" t="n">
         <v>25</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -2299,97 +2366,97 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
         <v>11</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>0.611</v>
+        <v>0.647</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>34</v>
+        <v>34.2</v>
       </c>
       <c r="J11" t="n">
-        <v>79.3</v>
+        <v>79.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.429</v>
+        <v>0.43</v>
       </c>
       <c r="L11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="M11" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0.359</v>
+        <v>0.35</v>
       </c>
       <c r="O11" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="P11" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.819</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="R11" t="n">
         <v>10.6</v>
       </c>
       <c r="S11" t="n">
-        <v>32.5</v>
+        <v>32.8</v>
       </c>
       <c r="T11" t="n">
-        <v>43.1</v>
+        <v>43.4</v>
       </c>
       <c r="U11" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="V11" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="W11" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X11" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA11" t="n">
         <v>20.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>94.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AI11" t="n">
         <v>29</v>
@@ -2398,22 +2465,22 @@
         <v>17</v>
       </c>
       <c r="AK11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ11" t="n">
         <v>2</v>
@@ -2422,25 +2489,25 @@
         <v>20</v>
       </c>
       <c r="AS11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT11" t="n">
         <v>6</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>9</v>
       </c>
       <c r="AU11" t="n">
         <v>26</v>
       </c>
       <c r="AV11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AW11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY11" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AZ11" t="n">
         <v>2</v>
@@ -2452,7 +2519,7 @@
         <v>24</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -2565,13 +2632,13 @@
         <v>22</v>
       </c>
       <c r="AF12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI12" t="n">
         <v>7</v>
@@ -2580,16 +2647,16 @@
         <v>5</v>
       </c>
       <c r="AK12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL12" t="n">
         <v>9</v>
       </c>
       <c r="AM12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
         <v>27</v>
@@ -2598,7 +2665,7 @@
         <v>29</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
         <v>9</v>
@@ -2607,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="AT12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU12" t="n">
         <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AW12" t="n">
         <v>25</v>
@@ -2622,7 +2689,7 @@
         <v>4</v>
       </c>
       <c r="AY12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
         <v>28</v>
@@ -2634,7 +2701,7 @@
         <v>10</v>
       </c>
       <c r="BC12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2823,7 @@
         <v>10</v>
       </c>
       <c r="AI13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ13" t="n">
         <v>9</v>
@@ -2765,7 +2832,7 @@
         <v>29</v>
       </c>
       <c r="AL13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AM13" t="n">
         <v>15</v>
@@ -2777,7 +2844,7 @@
         <v>29</v>
       </c>
       <c r="AP13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ13" t="n">
         <v>29</v>
@@ -2792,7 +2859,7 @@
         <v>22</v>
       </c>
       <c r="AU13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV13" t="n">
         <v>18</v>
@@ -2804,10 +2871,10 @@
         <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -2860,67 +2927,67 @@
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>41.1</v>
+        <v>40.4</v>
       </c>
       <c r="J14" t="n">
-        <v>88.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.466</v>
+        <v>0.463</v>
       </c>
       <c r="L14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="M14" t="n">
-        <v>18.1</v>
+        <v>17.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.362</v>
+        <v>0.386</v>
       </c>
       <c r="O14" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="P14" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R14" t="n">
-        <v>14.1</v>
+        <v>13.6</v>
       </c>
       <c r="S14" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="T14" t="n">
-        <v>47.3</v>
+        <v>46.9</v>
       </c>
       <c r="U14" t="n">
-        <v>23.5</v>
+        <v>22.4</v>
       </c>
       <c r="V14" t="n">
-        <v>13.6</v>
+        <v>13.4</v>
       </c>
       <c r="W14" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="X14" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.6</v>
+        <v>107.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>13.3</v>
+        <v>13.8</v>
       </c>
       <c r="AD14" t="n">
         <v>29</v>
@@ -2944,25 +3011,25 @@
         <v>2</v>
       </c>
       <c r="AK14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AM14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AN14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AO14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP14" t="n">
         <v>7</v>
       </c>
       <c r="AQ14" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR14" t="n">
         <v>2</v>
@@ -2974,16 +3041,16 @@
         <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
       </c>
       <c r="AX14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY14" t="n">
         <v>12</v>
@@ -2992,7 +3059,7 @@
         <v>5</v>
       </c>
       <c r="BA14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3135,22 +3202,22 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO15" t="n">
         <v>19</v>
       </c>
       <c r="AP15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT15" t="n">
         <v>23</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -3287,10 +3354,10 @@
         <v>1.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF16" t="n">
         <v>18</v>
@@ -3302,7 +3369,7 @@
         <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ16" t="n">
         <v>13</v>
@@ -3311,10 +3378,10 @@
         <v>13</v>
       </c>
       <c r="AL16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN16" t="n">
         <v>17</v>
@@ -3323,7 +3390,7 @@
         <v>25</v>
       </c>
       <c r="AP16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ16" t="n">
         <v>25</v>
@@ -3338,7 +3405,7 @@
         <v>29</v>
       </c>
       <c r="AU16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV16" t="n">
         <v>1</v>
@@ -3350,7 +3417,7 @@
         <v>10</v>
       </c>
       <c r="AY16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ16" t="n">
         <v>9</v>
@@ -3359,10 +3426,10 @@
         <v>25</v>
       </c>
       <c r="BB16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -3391,28 +3458,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E17" t="n">
         <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G17" t="n">
-        <v>0.389</v>
+        <v>0.368</v>
       </c>
       <c r="H17" t="n">
         <v>48.8</v>
       </c>
       <c r="I17" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="J17" t="n">
-        <v>81.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.427</v>
+        <v>0.429</v>
       </c>
       <c r="L17" t="n">
         <v>4.9</v>
@@ -3421,34 +3488,34 @@
         <v>14.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.345</v>
+        <v>0.349</v>
       </c>
       <c r="O17" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
       <c r="P17" t="n">
-        <v>26.3</v>
+        <v>26</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="R17" t="n">
         <v>13.2</v>
       </c>
       <c r="S17" t="n">
-        <v>31.5</v>
+        <v>30.8</v>
       </c>
       <c r="T17" t="n">
-        <v>44.7</v>
+        <v>44</v>
       </c>
       <c r="U17" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V17" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="W17" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="X17" t="n">
         <v>3.5</v>
@@ -3457,28 +3524,28 @@
         <v>5.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.9</v>
+        <v>23.6</v>
       </c>
       <c r="AB17" t="n">
         <v>95</v>
       </c>
       <c r="AC17" t="n">
-        <v>-1.8</v>
+        <v>-2.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
       </c>
       <c r="AF17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG17" t="n">
         <v>22</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>21</v>
       </c>
       <c r="AH17" t="n">
         <v>2</v>
@@ -3493,46 +3560,46 @@
         <v>28</v>
       </c>
       <c r="AL17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AM17" t="n">
         <v>26</v>
       </c>
       <c r="AN17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR17" t="n">
         <v>4</v>
       </c>
       <c r="AS17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AT17" t="n">
         <v>5</v>
       </c>
       <c r="AU17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AW17" t="n">
         <v>27</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>28</v>
       </c>
       <c r="AX17" t="n">
         <v>27</v>
       </c>
       <c r="AY17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ17" t="n">
         <v>29</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-3</v>
       </c>
       <c r="AD18" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE18" t="n">
         <v>26</v>
@@ -3675,16 +3742,16 @@
         <v>23</v>
       </c>
       <c r="AL18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM18" t="n">
         <v>23</v>
       </c>
       <c r="AN18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP18" t="n">
         <v>23</v>
@@ -3696,16 +3763,16 @@
         <v>10</v>
       </c>
       <c r="AS18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU18" t="n">
         <v>2</v>
       </c>
       <c r="AV18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW18" t="n">
         <v>29</v>
@@ -3714,19 +3781,19 @@
         <v>21</v>
       </c>
       <c r="AY18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ18" t="n">
         <v>27</v>
       </c>
       <c r="BA18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB18" t="n">
         <v>18</v>
       </c>
       <c r="BC18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -3755,94 +3822,94 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="n">
         <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.533</v>
       </c>
       <c r="H19" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I19" t="n">
-        <v>36.2</v>
+        <v>35.9</v>
       </c>
       <c r="J19" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="K19" t="n">
-        <v>0.447</v>
+        <v>0.444</v>
       </c>
       <c r="L19" t="n">
         <v>7.3</v>
       </c>
       <c r="M19" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0.374</v>
+        <v>0.375</v>
       </c>
       <c r="O19" t="n">
-        <v>22.2</v>
+        <v>21.7</v>
       </c>
       <c r="P19" t="n">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.775</v>
+        <v>0.765</v>
       </c>
       <c r="R19" t="n">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="S19" t="n">
-        <v>29.3</v>
+        <v>29.7</v>
       </c>
       <c r="T19" t="n">
-        <v>40.6</v>
+        <v>41.4</v>
       </c>
       <c r="U19" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="V19" t="n">
         <v>13.3</v>
       </c>
       <c r="W19" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="X19" t="n">
         <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>25.8</v>
+        <v>26.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AB19" t="n">
-        <v>101.9</v>
+        <v>100.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.4</v>
+        <v>-3.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AE19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF19" t="n">
         <v>12</v>
       </c>
-      <c r="AF19" t="n">
-        <v>10</v>
-      </c>
       <c r="AG19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH19" t="n">
         <v>3</v>
@@ -3854,16 +3921,16 @@
         <v>14</v>
       </c>
       <c r="AK19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO19" t="n">
         <v>4</v>
@@ -3872,43 +3939,43 @@
         <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AR19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AS19" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AT19" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AU19" t="n">
         <v>24</v>
       </c>
       <c r="AV19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX19" t="n">
         <v>18</v>
       </c>
       <c r="AY19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ19" t="n">
         <v>30</v>
       </c>
       <c r="BA19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB19" t="n">
         <v>5</v>
       </c>
       <c r="BC19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>3.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE20" t="n">
         <v>12</v>
@@ -4030,13 +4097,13 @@
         <v>30</v>
       </c>
       <c r="AI20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ20" t="n">
         <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AL20" t="n">
         <v>6</v>
@@ -4048,13 +4115,13 @@
         <v>4</v>
       </c>
       <c r="AO20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="n">
         <v>27</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR20" t="n">
         <v>27</v>
@@ -4069,7 +4136,7 @@
         <v>16</v>
       </c>
       <c r="AV20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AW20" t="n">
         <v>8</v>
@@ -4078,7 +4145,7 @@
         <v>26</v>
       </c>
       <c r="AY20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ20" t="n">
         <v>15</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -4200,13 +4267,13 @@
         <v>15</v>
       </c>
       <c r="AE21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH21" t="n">
         <v>10</v>
@@ -4227,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO21" t="n">
         <v>24</v>
@@ -4245,7 +4312,7 @@
         <v>7</v>
       </c>
       <c r="AT21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU21" t="n">
         <v>3</v>
@@ -4260,7 +4327,7 @@
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ21" t="n">
         <v>6</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-11.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>29</v>
@@ -4409,34 +4476,34 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP22" t="n">
         <v>14</v>
       </c>
       <c r="AQ22" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AR22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT22" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AU22" t="n">
         <v>27</v>
       </c>
       <c r="AV22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX22" t="n">
         <v>24</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>6.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE23" t="n">
         <v>3</v>
@@ -4576,13 +4643,13 @@
         <v>14</v>
       </c>
       <c r="AI23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ23" t="n">
         <v>22</v>
       </c>
       <c r="AK23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL23" t="n">
         <v>4</v>
@@ -4591,7 +4658,7 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO23" t="n">
         <v>5</v>
@@ -4609,7 +4676,7 @@
         <v>4</v>
       </c>
       <c r="AT23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU23" t="n">
         <v>28</v>
@@ -4624,19 +4691,19 @@
         <v>2</v>
       </c>
       <c r="AY23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ23" t="n">
         <v>11</v>
       </c>
       <c r="BA23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BC23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -4665,94 +4732,94 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E24" t="n">
         <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G24" t="n">
-        <v>0.412</v>
+        <v>0.438</v>
       </c>
       <c r="H24" t="n">
         <v>48</v>
       </c>
       <c r="I24" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J24" t="n">
-        <v>84</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K24" t="n">
         <v>0.436</v>
       </c>
       <c r="L24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="M24" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0.335</v>
+        <v>0.332</v>
       </c>
       <c r="O24" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P24" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.736</v>
+        <v>0.733</v>
       </c>
       <c r="R24" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="S24" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="T24" t="n">
-        <v>46.1</v>
+        <v>46.6</v>
       </c>
       <c r="U24" t="n">
-        <v>20.3</v>
+        <v>19.8</v>
       </c>
       <c r="V24" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="W24" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="X24" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="Y24" t="n">
         <v>5.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>93.90000000000001</v>
+        <v>94</v>
       </c>
       <c r="AC24" t="n">
-        <v>-0.4</v>
+        <v>0.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AE24" t="n">
         <v>19</v>
       </c>
       <c r="AF24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH24" t="n">
         <v>21</v>
@@ -4773,13 +4840,13 @@
         <v>28</v>
       </c>
       <c r="AN24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO24" t="n">
         <v>28</v>
       </c>
       <c r="AP24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
@@ -4791,19 +4858,19 @@
         <v>8</v>
       </c>
       <c r="AT24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AU24" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AV24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AY24" t="n">
         <v>24</v>
@@ -4818,7 +4885,7 @@
         <v>25</v>
       </c>
       <c r="BC24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -4847,100 +4914,100 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E25" t="n">
         <v>11</v>
       </c>
       <c r="F25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>0.611</v>
+        <v>0.647</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
       </c>
       <c r="I25" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J25" t="n">
-        <v>74</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.503</v>
+        <v>0.5</v>
       </c>
       <c r="L25" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="M25" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0.389</v>
+        <v>0.379</v>
       </c>
       <c r="O25" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="P25" t="n">
-        <v>26.3</v>
+        <v>26.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.741</v>
+        <v>0.74</v>
       </c>
       <c r="R25" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T25" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="U25" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V25" t="n">
-        <v>16.9</v>
+        <v>16.6</v>
       </c>
       <c r="W25" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X25" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y25" t="n">
         <v>4.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="n">
         <v>21.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>100.6</v>
+        <v>100.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI25" t="n">
         <v>10</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>9</v>
       </c>
       <c r="AJ25" t="n">
         <v>30</v>
@@ -4949,16 +5016,16 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM25" t="n">
         <v>16</v>
       </c>
       <c r="AN25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP25" t="n">
         <v>8</v>
@@ -4970,13 +5037,13 @@
         <v>30</v>
       </c>
       <c r="AS25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT25" t="n">
         <v>24</v>
       </c>
       <c r="AU25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AV25" t="n">
         <v>30</v>
@@ -4985,7 +5052,7 @@
         <v>26</v>
       </c>
       <c r="AX25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY25" t="n">
         <v>8</v>
@@ -4994,13 +5061,13 @@
         <v>7</v>
       </c>
       <c r="BA25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BC25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -5032,130 +5099,130 @@
         <v>17</v>
       </c>
       <c r="E26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>0.706</v>
+        <v>0.647</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36.6</v>
+        <v>36.2</v>
       </c>
       <c r="J26" t="n">
-        <v>78.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.466</v>
+        <v>0.456</v>
       </c>
       <c r="L26" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>20.8</v>
+        <v>21.2</v>
       </c>
       <c r="N26" t="n">
         <v>0.414</v>
       </c>
       <c r="O26" t="n">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="P26" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.77</v>
+        <v>0.765</v>
       </c>
       <c r="R26" t="n">
         <v>13.1</v>
       </c>
       <c r="S26" t="n">
-        <v>27.2</v>
+        <v>27.7</v>
       </c>
       <c r="T26" t="n">
-        <v>40.3</v>
+        <v>40.8</v>
       </c>
       <c r="U26" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="V26" t="n">
         <v>13.1</v>
       </c>
       <c r="W26" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="X26" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.7</v>
+        <v>98.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>6.9</v>
+        <v>5.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE26" t="n">
         <v>5</v>
       </c>
       <c r="AF26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH26" t="n">
         <v>14</v>
       </c>
       <c r="AI26" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AJ26" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AK26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AL26" t="n">
         <v>3</v>
       </c>
       <c r="AM26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN26" t="n">
         <v>2</v>
       </c>
       <c r="AO26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR26" t="n">
         <v>5</v>
       </c>
       <c r="AS26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU26" t="n">
         <v>8</v>
@@ -5164,25 +5231,25 @@
         <v>4</v>
       </c>
       <c r="AW26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY26" t="n">
         <v>1</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA26" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BB26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5383,7 @@
         <v>22</v>
       </c>
       <c r="AM27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AN27" t="n">
         <v>29</v>
@@ -5355,10 +5422,10 @@
         <v>11</v>
       </c>
       <c r="AZ27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB27" t="n">
         <v>16</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -5477,16 +5544,16 @@
         <v>12</v>
       </c>
       <c r="AF28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AG28" t="n">
         <v>13</v>
       </c>
       <c r="AH28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI28" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AJ28" t="n">
         <v>26</v>
@@ -5498,7 +5565,7 @@
         <v>5</v>
       </c>
       <c r="AM28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN28" t="n">
         <v>5</v>
@@ -5519,22 +5586,22 @@
         <v>13</v>
       </c>
       <c r="AT28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU28" t="n">
         <v>13</v>
       </c>
       <c r="AV28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW28" t="n">
         <v>30</v>
       </c>
       <c r="AX28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ28" t="n">
         <v>3</v>
@@ -5546,7 +5613,7 @@
         <v>26</v>
       </c>
       <c r="BC28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -5575,121 +5642,121 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E29" t="n">
         <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="H29" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I29" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="J29" t="n">
-        <v>78</v>
+        <v>77.3</v>
       </c>
       <c r="K29" t="n">
-        <v>0.456</v>
+        <v>0.461</v>
       </c>
       <c r="L29" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="M29" t="n">
-        <v>16.4</v>
+        <v>15.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0.407</v>
+        <v>0.403</v>
       </c>
       <c r="O29" t="n">
         <v>20.2</v>
       </c>
       <c r="P29" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.835</v>
+        <v>0.839</v>
       </c>
       <c r="R29" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>30</v>
+        <v>30.3</v>
       </c>
       <c r="T29" t="n">
-        <v>38.9</v>
+        <v>39.1</v>
       </c>
       <c r="U29" t="n">
         <v>23.1</v>
       </c>
       <c r="V29" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W29" t="n">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
       <c r="X29" t="n">
         <v>5.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>98</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.7</v>
+        <v>-0.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AE29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AG29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH29" t="n">
         <v>3</v>
       </c>
       <c r="AI29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AL29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AN29" t="n">
         <v>3</v>
       </c>
       <c r="AO29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5698,19 +5765,19 @@
         <v>28</v>
       </c>
       <c r="AS29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV29" t="n">
         <v>14</v>
       </c>
       <c r="AW29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX29" t="n">
         <v>13</v>
@@ -5722,7 +5789,7 @@
         <v>1</v>
       </c>
       <c r="BA29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB29" t="n">
         <v>15</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -5835,16 +5902,16 @@
         <v>3.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF30" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AG30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AH30" t="n">
         <v>21</v>
@@ -5853,7 +5920,7 @@
         <v>5</v>
       </c>
       <c r="AJ30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK30" t="n">
         <v>2</v>
@@ -5868,13 +5935,13 @@
         <v>12</v>
       </c>
       <c r="AO30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP30" t="n">
         <v>12</v>
       </c>
       <c r="AQ30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR30" t="n">
         <v>7</v>
@@ -5883,7 +5950,7 @@
         <v>25</v>
       </c>
       <c r="AT30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
@@ -5910,7 +5977,7 @@
         <v>9</v>
       </c>
       <c r="BC30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
@@ -6023,7 +6090,7 @@
         <v>29</v>
       </c>
       <c r="AF31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
@@ -6032,7 +6099,7 @@
         <v>9</v>
       </c>
       <c r="AI31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AJ31" t="n">
         <v>10</v>
@@ -6044,13 +6111,13 @@
         <v>26</v>
       </c>
       <c r="AM31" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AN31" t="n">
         <v>30</v>
       </c>
       <c r="AO31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP31" t="n">
         <v>13</v>
@@ -6065,13 +6132,13 @@
         <v>24</v>
       </c>
       <c r="AT31" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AU31" t="n">
         <v>23</v>
       </c>
       <c r="AV31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW31" t="n">
         <v>7</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-30-2008-09</t>
+          <t>2008-11-30</t>
         </is>
       </c>
     </row>
